--- a/Result/profitability/2301.xlsx
+++ b/Result/profitability/2301.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.3</v>
       </c>
       <c r="M2" t="n">
-        <v>1.4275</v>
+        <v>1.635</v>
       </c>
       <c r="N2" t="n">
-        <v>20.96</v>
+        <v>21.5575</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.64</v>
       </c>
       <c r="M3" t="n">
-        <v>1.3225</v>
+        <v>1.54875</v>
       </c>
       <c r="N3" t="n">
-        <v>20.02125</v>
+        <v>20.76625</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.95</v>
       </c>
       <c r="M4" t="n">
-        <v>1.275</v>
+        <v>1.47875</v>
       </c>
       <c r="N4" t="n">
-        <v>19.1475</v>
+        <v>19.7275</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.15</v>
       </c>
       <c r="M5" t="n">
-        <v>1.105</v>
+        <v>1.32375</v>
       </c>
       <c r="N5" t="n">
-        <v>18.14375</v>
+        <v>18.78125</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.17</v>
       </c>
       <c r="M6" t="n">
-        <v>0.9524999999999999</v>
+        <v>1.08875</v>
       </c>
       <c r="N6" t="n">
-        <v>17.1775</v>
+        <v>17.45</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,13 +1264,13 @@
         <v>0.75</v>
       </c>
       <c r="M7" t="n">
-        <v>0.79</v>
+        <v>0.97</v>
       </c>
       <c r="N7" t="n">
-        <v>15.945</v>
+        <v>16.6325</v>
       </c>
       <c r="O7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
         <v>1</v>
@@ -1282,7 +1282,7 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>1.13</v>
       </c>
       <c r="M8" t="n">
-        <v>0.71875</v>
+        <v>0.9037499999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>15.4</v>
+        <v>16.095</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1518,7 +1518,7 @@
         <v>1.16</v>
       </c>
       <c r="M9" t="n">
-        <v>0.6562499999999999</v>
+        <v>0.65625</v>
       </c>
       <c r="N9" t="n">
         <v>14.87375</v>
@@ -1899,7 +1899,7 @@
         <v>1.14</v>
       </c>
       <c r="M12" t="n">
-        <v>0.8049999999999999</v>
+        <v>0.805</v>
       </c>
       <c r="N12" t="n">
         <v>15.8425</v>
@@ -2026,7 +2026,7 @@
         <v>0.99</v>
       </c>
       <c r="M13" t="n">
-        <v>0.91</v>
+        <v>0.9099999999999999</v>
       </c>
       <c r="N13" t="n">
         <v>15.9275</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2301</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>52703</v>
+      </c>
+      <c r="D75" t="n">
+        <v>38355</v>
+      </c>
+      <c r="E75" t="n">
+        <v>14348</v>
+      </c>
+      <c r="F75" t="n">
+        <v>27.22</v>
+      </c>
+      <c r="G75" t="n">
+        <v>8203</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>15.56%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>1166</v>
+      </c>
+      <c r="J75" t="n">
+        <v>9368</v>
+      </c>
+      <c r="K75" t="n">
+        <v>7116</v>
+      </c>
+      <c r="L75" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="M75" t="n">
+        <v>1.7825</v>
+      </c>
+      <c r="N75" t="n">
+        <v>23.005</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>1</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.8915662650602412</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>5.559999999999999</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.2566943674976916</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>1.258992805755396</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>5.099999999999998</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.2305605786618443</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
